--- a/ksoft/docs/records/Item_Family_Commercial_Records.xlsx
+++ b/ksoft/docs/records/Item_Family_Commercial_Records.xlsx
@@ -1774,13 +1774,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2267C0C-FBC9-458E-ACC9-3E0428233C7E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA575D66-5521-43CD-9FBB-09BDF7A045D5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4262C9A-EB31-4DF6-BFFE-F1B38A6CEB60}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2046E91-04D4-48AB-AEC7-6E18B1D8CF56}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6D97618-C58E-4F0A-A099-A463C22CE035}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F5D6CE5-5539-420F-B840-C146D8663BDA}"/>
 </file>
--- a/ksoft/docs/records/Item_Family_Commercial_Records.xlsx
+++ b/ksoft/docs/records/Item_Family_Commercial_Records.xlsx
@@ -1774,13 +1774,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA575D66-5521-43CD-9FBB-09BDF7A045D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2267C0C-FBC9-458E-ACC9-3E0428233C7E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2046E91-04D4-48AB-AEC7-6E18B1D8CF56}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4262C9A-EB31-4DF6-BFFE-F1B38A6CEB60}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F5D6CE5-5539-420F-B840-C146D8663BDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6D97618-C58E-4F0A-A099-A463C22CE035}"/>
 </file>